--- a/artfynd/A 21986-2023 artfynd.xlsx
+++ b/artfynd/A 21986-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4692,37 +4692,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>93753089</v>
+        <v>137486589</v>
       </c>
       <c r="B33" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4730,24 +4730,20 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>505029</v>
+        <v>505101</v>
       </c>
       <c r="R33" t="n">
-        <v>6611313</v>
+        <v>6611093</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4771,12 +4767,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4790,17 +4786,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4811,7 +4807,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4821,43 +4817,43 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93753089</t>
+          <t>https://artportalen.se/Sighting/137486589</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>93753090</v>
+        <v>137486590</v>
       </c>
       <c r="B34" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4865,24 +4861,20 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>505024</v>
+        <v>505092</v>
       </c>
       <c r="R34" t="n">
-        <v>6611319</v>
+        <v>6611195</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4906,12 +4898,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4925,17 +4917,17 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4946,7 +4938,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4956,43 +4948,43 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93753090</t>
+          <t>https://artportalen.se/Sighting/137486590</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>93753092</v>
+        <v>137486626</v>
       </c>
       <c r="B35" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5000,24 +4992,20 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>505037</v>
+        <v>505111</v>
       </c>
       <c r="R35" t="n">
-        <v>6611330</v>
+        <v>6611043</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5041,12 +5029,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5060,17 +5048,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5081,7 +5069,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -5091,43 +5079,43 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93753092</t>
+          <t>https://artportalen.se/Sighting/137486626</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>93753093</v>
+        <v>137486628</v>
       </c>
       <c r="B36" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5135,24 +5123,20 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>505030</v>
+        <v>505110</v>
       </c>
       <c r="R36" t="n">
-        <v>6611329</v>
+        <v>6611043</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5176,12 +5160,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5195,17 +5179,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5216,7 +5200,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5226,38 +5210,38 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93753093</t>
+          <t>https://artportalen.se/Sighting/137486628</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>97080374</v>
+        <v>137486742</v>
       </c>
       <c r="B37" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5270,16 +5254,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:15, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>505059</v>
+        <v>505107</v>
       </c>
       <c r="R37" t="n">
-        <v>6611238</v>
+        <v>6611054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5306,17 +5291,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupna och delvis nerramlat.</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5330,17 +5310,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5351,7 +5331,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5361,43 +5341,43 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080374</t>
+          <t>https://artportalen.se/Sighting/137486742</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>97080375</v>
+        <v>137486743</v>
       </c>
       <c r="B38" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5405,16 +5385,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:15, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>505055</v>
+        <v>505107</v>
       </c>
       <c r="R38" t="n">
-        <v>6611246</v>
+        <v>6611045</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5441,17 +5422,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupen och delvis nerramlad.</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5465,17 +5441,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5486,7 +5462,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5496,43 +5472,43 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080375</t>
+          <t>https://artportalen.se/Sighting/137486743</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>97080376</v>
+        <v>137486746</v>
       </c>
       <c r="B39" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5540,16 +5516,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>505029</v>
+        <v>505094</v>
       </c>
       <c r="R39" t="n">
-        <v>6611314</v>
+        <v>6611188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5576,17 +5553,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupen.</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5600,17 +5572,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5621,7 +5593,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5631,43 +5603,43 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080376</t>
+          <t>https://artportalen.se/Sighting/137486746</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>97080378</v>
+        <v>137486747</v>
       </c>
       <c r="B40" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5675,16 +5647,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>505022</v>
+        <v>505094</v>
       </c>
       <c r="R40" t="n">
-        <v>6611319</v>
+        <v>6611186</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,17 +5684,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupen.</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5735,17 +5703,17 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5756,7 +5724,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5766,43 +5734,43 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080378</t>
+          <t>https://artportalen.se/Sighting/137486747</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>97080384</v>
+        <v>137488093</v>
       </c>
       <c r="B41" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5810,16 +5778,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>505036</v>
+        <v>505113</v>
       </c>
       <c r="R41" t="n">
-        <v>6611331</v>
+        <v>6611037</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5846,17 +5815,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupna.</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5870,17 +5834,17 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>ängsvädd</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Succisa pratensis</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5891,7 +5855,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5901,38 +5865,38 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080384</t>
+          <t>https://artportalen.se/Sighting/137488093</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>97080386</v>
+        <v>137488112</v>
       </c>
       <c r="B42" t="n">
-        <v>43428</v>
+        <v>43485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100943</v>
+        <v>100942</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asknätfjäril</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Euphydryas maturna</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5945,16 +5909,17 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:22, Vstm</t>
+          <t>Körartorp Yta 4:3 Ledningsgatan, Vstm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>505030</v>
+        <v>505039</v>
       </c>
       <c r="R42" t="n">
-        <v>6611327</v>
+        <v>6611325</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5981,17 +5946,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupen.</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6005,17 +5965,17 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>åkervädd</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Knautia arvensis</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Knautia arvensis</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6026,7 +5986,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Inger Holst</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -6036,13 +5996,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080386</t>
+          <t>https://artportalen.se/Sighting/137488112</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>97080387</v>
+        <v>93753089</v>
       </c>
       <c r="B43" t="n">
         <v>43428</v>
@@ -6080,19 +6040,24 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Körartorp yta 1:22, Vstm</t>
+          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>505025</v>
+        <v>505029</v>
       </c>
       <c r="R43" t="n">
-        <v>6611333</v>
+        <v>6611313</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6116,17 +6081,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Larvstadie 3. Urkrupen.</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6171,13 +6131,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97080387</t>
+          <t>https://artportalen.se/Sighting/93753089</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105555035</v>
+        <v>93753090</v>
       </c>
       <c r="B44" t="n">
         <v>43428</v>
@@ -6215,19 +6175,24 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>505029</v>
+        <v>505024</v>
       </c>
       <c r="R44" t="n">
-        <v>6611327</v>
+        <v>6611319</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6251,17 +6216,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6306,13 +6266,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555035</t>
+          <t>https://artportalen.se/Sighting/93753090</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105555037</v>
+        <v>93753092</v>
       </c>
       <c r="B45" t="n">
         <v>43428</v>
@@ -6350,19 +6310,24 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>505036</v>
+        <v>505037</v>
       </c>
       <c r="R45" t="n">
         <v>6611330</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6386,17 +6351,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6441,13 +6401,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555037</t>
+          <t>https://artportalen.se/Sighting/93753092</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>105555039</v>
+        <v>93753093</v>
       </c>
       <c r="B46" t="n">
         <v>43428</v>
@@ -6485,19 +6445,24 @@
           <t>kolonier</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Leja-Dyrkatorp inklusive Nyskogen och Körartorp Delyta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>505037</v>
+        <v>505030</v>
       </c>
       <c r="R46" t="n">
-        <v>6611315</v>
+        <v>6611329</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6521,17 +6486,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>2020-09-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6576,13 +6536,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555039</t>
+          <t>https://artportalen.se/Sighting/93753093</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>105555042</v>
+        <v>97080374</v>
       </c>
       <c r="B47" t="n">
         <v>43428</v>
@@ -6612,7 +6572,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6622,14 +6582,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:15, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>505028</v>
+        <v>505059</v>
       </c>
       <c r="R47" t="n">
-        <v>6611330</v>
+        <v>6611238</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6656,17 +6616,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>Larvstadie 3. Urkrupna och delvis nerramlat.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6711,13 +6671,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555042</t>
+          <t>https://artportalen.se/Sighting/97080374</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>105555090</v>
+        <v>97080375</v>
       </c>
       <c r="B48" t="n">
         <v>43428</v>
@@ -6747,7 +6707,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6757,14 +6717,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:15, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>505054</v>
+        <v>505055</v>
       </c>
       <c r="R48" t="n">
-        <v>6611242</v>
+        <v>6611246</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6791,17 +6751,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>Larvstadie 3. Urkrupen och delvis nerramlad.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6846,13 +6806,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555090</t>
+          <t>https://artportalen.se/Sighting/97080375</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>105555091</v>
+        <v>97080376</v>
       </c>
       <c r="B49" t="n">
         <v>43428</v>
@@ -6882,7 +6842,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6892,14 +6852,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>505060</v>
+        <v>505029</v>
       </c>
       <c r="R49" t="n">
-        <v>6611258</v>
+        <v>6611314</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6926,17 +6886,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>Larvstadie 3. Urkrupen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6981,13 +6941,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555091</t>
+          <t>https://artportalen.se/Sighting/97080376</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>105555092</v>
+        <v>97080378</v>
       </c>
       <c r="B50" t="n">
         <v>43428</v>
@@ -7027,14 +6987,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>505063</v>
+        <v>505022</v>
       </c>
       <c r="R50" t="n">
-        <v>6611238</v>
+        <v>6611319</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7061,17 +7021,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>Larvstadie 3. Urkrupen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7116,13 +7076,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555092</t>
+          <t>https://artportalen.se/Sighting/97080378</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>105555093</v>
+        <v>97080384</v>
       </c>
       <c r="B51" t="n">
         <v>43428</v>
@@ -7152,7 +7112,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7162,14 +7122,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>505062</v>
+        <v>505036</v>
       </c>
       <c r="R51" t="n">
-        <v>6611238</v>
+        <v>6611331</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7196,17 +7156,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
+          <t>Larvstadie 3. Urkrupna.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7251,13 +7211,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105555093</t>
+          <t>https://artportalen.se/Sighting/97080384</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113473527</v>
+        <v>97080386</v>
       </c>
       <c r="B52" t="n">
         <v>43428</v>
@@ -7297,14 +7257,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>505031</v>
+        <v>505030</v>
       </c>
       <c r="R52" t="n">
-        <v>6611326</v>
+        <v>6611327</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7331,12 +7291,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Larvstadie 3. Urkrupen.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7381,13 +7346,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113473527</t>
+          <t>https://artportalen.se/Sighting/97080386</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120766223</v>
+        <v>97080387</v>
       </c>
       <c r="B53" t="n">
         <v>43428</v>
@@ -7425,21 +7390,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Körartorp yta 1:22, Vstm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>505032</v>
+        <v>505025</v>
       </c>
       <c r="R53" t="n">
-        <v>6611297</v>
+        <v>6611333</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7466,12 +7426,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Larvstadie 3. Urkrupen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7516,13 +7481,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120766223</t>
+          <t>https://artportalen.se/Sighting/97080387</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120766224</v>
+        <v>105555035</v>
       </c>
       <c r="B54" t="n">
         <v>43428</v>
@@ -7560,21 +7525,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>505053</v>
+        <v>505029</v>
       </c>
       <c r="R54" t="n">
-        <v>6611286</v>
+        <v>6611327</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7601,12 +7561,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7651,13 +7616,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120766224</t>
+          <t>https://artportalen.se/Sighting/105555035</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120766225</v>
+        <v>105555037</v>
       </c>
       <c r="B55" t="n">
         <v>43428</v>
@@ -7695,21 +7660,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>505027</v>
+        <v>505036</v>
       </c>
       <c r="R55" t="n">
-        <v>6611316</v>
+        <v>6611330</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7736,12 +7696,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7786,13 +7751,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120766225</t>
+          <t>https://artportalen.se/Sighting/105555037</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120766226</v>
+        <v>105555039</v>
       </c>
       <c r="B56" t="n">
         <v>43428</v>
@@ -7830,21 +7795,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>505030</v>
+        <v>505037</v>
       </c>
       <c r="R56" t="n">
-        <v>6611324</v>
+        <v>6611315</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7871,12 +7831,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7921,13 +7886,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120766226</t>
+          <t>https://artportalen.se/Sighting/105555039</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129833112</v>
+        <v>105555042</v>
       </c>
       <c r="B57" t="n">
         <v>43428</v>
@@ -7965,21 +7930,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>505064</v>
+        <v>505028</v>
       </c>
       <c r="R57" t="n">
-        <v>6611207</v>
+        <v>6611330</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8006,12 +7966,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8056,13 +8021,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129833112</t>
+          <t>https://artportalen.se/Sighting/105555042</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129833120</v>
+        <v>105555090</v>
       </c>
       <c r="B58" t="n">
         <v>43428</v>
@@ -8092,7 +8057,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8100,21 +8065,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>505035</v>
+        <v>505054</v>
       </c>
       <c r="R58" t="n">
-        <v>6611332</v>
+        <v>6611242</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8141,12 +8101,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8191,13 +8156,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129833120</t>
+          <t>https://artportalen.se/Sighting/105555090</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129833122</v>
+        <v>105555091</v>
       </c>
       <c r="B59" t="n">
         <v>43428</v>
@@ -8235,21 +8200,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>505051</v>
+        <v>505060</v>
       </c>
       <c r="R59" t="n">
-        <v>6611283</v>
+        <v>6611258</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8276,12 +8236,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8326,13 +8291,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129833122</t>
+          <t>https://artportalen.se/Sighting/105555091</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129833123</v>
+        <v>105555092</v>
       </c>
       <c r="B60" t="n">
         <v>43428</v>
@@ -8370,21 +8335,16 @@
           <t>kolonier</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>505034</v>
+        <v>505063</v>
       </c>
       <c r="R60" t="n">
-        <v>6611302</v>
+        <v>6611238</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8411,12 +8371,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8461,16 +8426,16 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129833123</t>
+          <t>https://artportalen.se/Sighting/105555092</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>96191167</v>
+        <v>105555093</v>
       </c>
       <c r="B61" t="n">
-        <v>106813</v>
+        <v>43428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8478,43 +8443,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Körartorp kraftledningsgatan, Vstm</t>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>505058</v>
+        <v>505062</v>
       </c>
       <c r="R61" t="n">
-        <v>6611259</v>
+        <v>6611238</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8541,17 +8506,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>1,5 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>Räkning av larvkolonier (spånader) inom Biogeografisk uppföljning av fjärilar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8562,31 +8527,50 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96191167</t>
+          <t>https://artportalen.se/Sighting/105555093</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>105404720</v>
+        <v>113473527</v>
       </c>
       <c r="B62" t="n">
-        <v>106813</v>
+        <v>43428</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8594,34 +8578,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Körartorp, Vstm</t>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>505060</v>
+        <v>505031</v>
       </c>
       <c r="R62" t="n">
-        <v>6611259</v>
+        <v>6611326</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8648,17 +8641,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>God förekomst. Dokumentation av asknätfjärilens värdväxter.</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8669,20 +8657,1866 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113473527</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120766223</v>
+      </c>
+      <c r="B63" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>505032</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6611297</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
         <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766223</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120766224</v>
+      </c>
+      <c r="B64" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>505053</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6611286</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766224</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120766225</v>
+      </c>
+      <c r="B65" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>505027</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6611316</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766225</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120766226</v>
+      </c>
+      <c r="B66" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>505030</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6611324</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120766226</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129833112</v>
+      </c>
+      <c r="B67" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>505064</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6611207</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833112</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129833120</v>
+      </c>
+      <c r="B68" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>505035</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6611332</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833120</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129833122</v>
+      </c>
+      <c r="B69" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>505051</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6611283</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833122</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129833123</v>
+      </c>
+      <c r="B70" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>505034</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6611302</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129833123</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137489508</v>
+      </c>
+      <c r="B71" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:22 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>505032</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6611332</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137489508</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137489902</v>
+      </c>
+      <c r="B72" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>505060</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6611260</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137489902</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137489903</v>
+      </c>
+      <c r="B73" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>505046</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6611244</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137489903</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137489904</v>
+      </c>
+      <c r="B74" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lejaområdet Yta 1:15 Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>505044</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6611246</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137489904</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>96191167</v>
+      </c>
+      <c r="B75" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Körartorp kraftledningsgatan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>505058</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6611259</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>1,5 m höga. Dokumentation av asknätfjärilens värdväxter.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96191167</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105404720</v>
+      </c>
+      <c r="B76" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Körartorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>505060</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6611259</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>God förekomst. Dokumentation av asknätfjärilens värdväxter.</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105404720</t>
         </is>
@@ -8751,6 +10585,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
